--- a/assets/docs/lop3/KHDH ca khoi - Lop 3.xlsx
+++ b/assets/docs/lop3/KHDH ca khoi - Lop 3.xlsx
@@ -612,7 +612,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Khởi động bài “- Nghe – viết: Em yêu mùa hè / -Phân biệt c/k”, GV chiếu tranh đồ vật trên máy chiếu để HS đoán tên chứa c hoặc k; trước khi viết
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài tập phân biệt c/k, GV chiếu bài tập tương tác điền c hoặc k vào chỗ trống (…á, …éo, …ính, …on); HS lên bấm chọn</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -808,7 +813,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Khởi động bài “- Nghe – viết: Cánh rừng trong nắng / -Phân biệt g/gh”, GV mở bài hát cho HS nghe và vận động; trước khi viết
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở phần vận dụng ghi nhật kí, GV chiếu một mẫu nhật kí ngắn trên tivi để HS quan sát cách ghi ngày, việc làm, cảm xúc</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1005,7 +1015,12 @@
           <t>17</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước khi nghe viết bài “Mặt trời nhỏ”, GV chiếu đoạn thơ phóng to và bấm tô màu những chữ dễ viết sai cùng các tiếng bắt đầu bằng ng, ngh; HS đọc thầm
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần phân biệt ng và ngh, GV mở bài tập tương tác chọn chữ đúng điền vào chỗ trống; máy báo đúng</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1201,7 +1216,12 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước khi nghe viết bài “Mùa hè lấp lánh”, GV chiếu đoạn thơ phóng to và bấm tô màu các chữ dễ viết sai cùng những tiếng có ch, tr, v, d
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần phân biệt ch với tr và v với d, GV mở bài tập tương tác chọn chữ đúng điền vào chỗ trống; máy báo đúng</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1396,7 +1416,9 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>QTE: QTE: liên hệ quyền được học tập, vui chơi và được yêu thương của trẻ em qua nhân vật, chi tiết trong bài đọc.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước khi nghe viết bài “Đi học vui sao”, GV chiếu đoạn thơ phóng to và bấm tô màu những tiếng có s, x cùng các tiếng mang dấu hỏi, dấu ngã
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần phân biệt s với x và dấu hỏi với dấu ngã, GV mở bài tập tương tác chọn chữ và dấu thanh đúng; máy báo đúng
+QTE: QTE: liên hệ quyền được học tập, vui chơi và được yêu thương của trẻ em qua nhân vật, chi tiết trong bài đọc.</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1528,9 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN trình bày suy nghĩ, bày tỏ cảm xúc của bản thân bằng lời lẽ phù hợp.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước khi đọc bài “Viết đoạn văn nêu tình cảm, cảm xúc đối với một người mà em yêu quý”, GV chiếu 2–3 hình ảnh hoặc một đoạn video ngắn về sự vật
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV mở bản đọc mẫu do phát thanh viên thể hiện cho HS nghe một lần, dừng lại để HS nhận ra chỗ người đọc ngắt hơi, nhấn giọng
+KNS: KN trình bày suy nghĩ, bày tỏ cảm xúc của bản thân bằng lời lẽ phù hợp.</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1609,12 @@
           <t>38</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước khi nghe viết đoạn trong bài “Lời giải toán đặc biệt”, GV chiếu đoạn văn phóng to và bấm tô màu các tiếng có r, d, gi cùng những tiếng vần an, ang
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần phân biệt r với d, gi và an với ang, GV mở bài tập tương tác chọn chữ và vần đúng; máy báo đúng</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1783,7 +1812,9 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước khi nghe viết bài “Nghe thầy đọc thơ”, GV chiếu đoạn thơ phóng to và bấm tô màu các tiếng bắt đầu bằng l, n cùng những tiếng có vần ăn, ăng
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần phân biệt l với n và ăn với ăng, GV mở bài tập tương tác chọn chữ, chọn vần đúng; máy báo đúng
+KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
     </row>
@@ -1977,7 +2008,12 @@
           <t>52</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước khi nghe viết bài “Thư viện”, GV chiếu đoạn văn phóng to và bấm tô màu các tiếng có ch, tr cùng những tiếng vần ân, âng; HS đọc thầm
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần phân biệt ch với tr và ân với âng, GV mở bài tập tương tác chọn chữ, chọn vần đúng; máy báo đúng</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -2233,7 +2269,12 @@
           <t>66</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước khi nghe viết bài “Đồ đạc trong nhà”, GV chiếu đoạn thơ phóng to và bấm tô màu các tiếng có vần iêu, ươu cùng những tiếng vần en, eng; HS đọc thầm
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần phân biệt iêu với ươu và en với eng, GV mở bài tập tương tác chọn vần đúng; máy báo đúng, sai ngay nên HS nhận ra lỗi phát âm của mình</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -2425,7 +2466,12 @@
           <t>73</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước khi nghe viết bài “Khi cả nhà bé tí”, GV chiếu đoạn thơ phóng to và bấm tô màu các tiếng có vần iu, ưu cùng những tiếng vần iên, iêng
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần phân biệt iu với ưu và iên với iêng, GV mở bài tập tương tác chọn vần đúng; máy báo đúng, sai ngay nên HS nhận ra lỗi phát âm của mình</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -2618,7 +2664,12 @@
           <t>80</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước khi nghe viết bài “Kho sách của ông bà”, GV chiếu đoạn văn phóng to và bấm tô màu các tiếng có s, x cùng những tiếng vần uôn, uông; HS đọc thầm
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần phân biệt s với x và uôn với uông, GV mở bài tập tương tác chọn chữ, chọn vần đúng; máy báo đúng</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -2810,7 +2861,12 @@
           <t>87</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước khi nghe viết bài “Tôi yêu em tôi”, GV chiếu đoạn thơ phóng to và bấm tô màu các tiếng có r, d, gi cùng những tiếng vần ươn, ương; HS đọc thầm
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần phân biệt r, d, gi và ươn với ương, GV mở bài tập tương tác chọn chữ, chọn vần đúng; máy báo đúng</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -3005,7 +3061,9 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN ứng xử: thể hiện sự quan tâm, lễ phép, biết nói lời cảm ơn và xin lỗi đúng lúc.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước khi nghe viết bài “Những bậc đá chạm mây”, GV chiếu đoạn văn phóng to và bấm tô màu những chữ viết hoa cùng các tiếng dễ viết sai; HS đọc thầm
+Năng lực số Miền 5 (Cơ bản, bậc 1): Sau khi viết, GV chiếu đoạn văn mẫu cho HS soát lỗi theo từng câu; các em tự đánh dấu chỗ mình sai
+KNS: KN ứng xử: thể hiện sự quan tâm, lễ phép, biết nói lời cảm ơn và xin lỗi đúng lúc.</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3257,12 @@
           <t>101</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nghe – viết bài thơ “Trong vườn”, GV chiếu bài thơ phóng to lên màn hình, tô sáng những tiếng dễ viết sai và mở bản đọc mẫu để HS nghe…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài tập phân biệt l/n và dấu hỏi, dấu ngã, GV mở bài tập tương tác trên máy chiếu: máy hiện từ còn thiếu</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -3392,7 +3455,12 @@
           <t>108</t>
         </is>
       </c>
-      <c r="H77" s="4" t="inlineStr"/>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nghe – viết bài thơ “Gió”, GV chiếu bài thơ phóng to lên màn hình, tô sáng những tiếng dễ viết sai và mở bản đọc mẫu để HS nghe rõ…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài tập phân biệt s/x và ao/au, GV mở bài tập tương tác trên máy chiếu: máy hiện từ còn thiếu chữ, HS chọn s hay x</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -3584,7 +3652,12 @@
           <t>115</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr"/>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nghe – viết bài “Người làm đồ chơi”, GV chiếu đoạn văn phóng to lên màn hình, tô sáng các tên riêng cần viết hoa và mở bản đọc mẫu để…
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Viết phiếu mượn sách, GV chiếu mẫu phiếu mượn sách của thư viện trường lên màn hình, cùng HS điền thử từng ô tên sách, tên tác giả</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -3845,7 +3918,12 @@
           <t>129</t>
         </is>
       </c>
-      <c r="H89" s="4" t="inlineStr"/>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nghe – viết bài “Buổi sáng”, GV chiếu bài thơ phóng to lên màn hình, tô sáng những tiếng dễ viết sai và mở bản đọc mẫu để HS nghe rõ…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài tập phân biệt ch/tr và at/ac, GV mở bài tập tương tác: máy hiện từ còn thiếu chữ, HS chọn ch hay tr, at hay ac rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -4039,7 +4117,9 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>QPAN: Liên hệ truyền thống chống giặc ngoại xâm, gương dũng cảm của thiếu niên, nhi đồng và Bà mẹ Việt Nam anh hùng; HS nêu được biển, đảo là một phần lãnh thổ thiêng liêng của Tổ quốc.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nghe – viết đoạn văn “Trăng trên biển”, GV chiếu đoạn văn phóng to lên màn hình, tô sáng những tiếng dễ viết sai và mở bản đọc mẫu để HS…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài tập phân biệt s/x và ăt/ăc, GV mở bài tập tương tác: máy hiện từ còn thiếu chữ, HS chọn s hay x, ăt hay ăc rồi bấm kiểm tra
+QPAN: Liên hệ truyền thống chống giặc ngoại xâm, gương dũng cảm của thiếu niên, nhi đồng và Bà mẹ Việt Nam anh hùng; HS nêu được biển, đảo là một phần lãnh thổ thiêng liêng của Tổ quốc.</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4314,12 @@
           <t>143</t>
         </is>
       </c>
-      <c r="H99" s="4" t="inlineStr"/>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nghe – viết bài “Chim chích bông”, GV chiếu bài viết phóng to lên màn hình, tô sáng các tên riêng địa lí cần viết hoa và mở bản đọc mẫu…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài tập phân biệt iêu/ươu và ât/âc, GV mở bài tập tương tác: máy hiện từ còn thiếu vần, HS chọn vần đúng rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -4426,7 +4511,12 @@
           <t>150</t>
         </is>
       </c>
-      <c r="H104" s="4" t="inlineStr"/>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nhớ – viết ba khổ thơ đầu bài “Mặt trời xanh của tôi”, GV chiếu bài thơ phóng to lên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài tập phân biệt r/d/gi và in/inh, GV mở bài tập tương tác: máy hiện từ còn thiếu chữ, HS chọn chữ hoặc vần đúng rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -4619,7 +4709,12 @@
           <t>157</t>
         </is>
       </c>
-      <c r="H109" s="4" t="inlineStr"/>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nghe – viết bài “Lời kêu gọi toàn dân tập thể dục”, GV chiếu đoạn viết phóng to lên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài tập phân biệt l/n và dấu hỏi, dấu ngã, GV mở bài tập tương tác: máy hiện từ còn thiếu chữ hoặc dấu thanh, HS chọn rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -4811,7 +4906,12 @@
           <t>164</t>
         </is>
       </c>
-      <c r="H114" s="4" t="inlineStr"/>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nghe – viết bài “Chuyện bên cửa sổ”, GV chiếu đoạn viết phóng to lên màn hình, tô sáng những tiếng dễ viết sai và mở bản đọc mẫu để HS…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài tập phân biệt iu/ưu và im/iêm, GV mở bài tập tương tác: máy hiện từ còn thiếu vần, HS chọn vần đúng rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -5004,7 +5104,12 @@
           <t>171</t>
         </is>
       </c>
-      <c r="H119" s="4" t="inlineStr"/>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nghe – viết bài “Bài học của gấu”, GV chiếu đoạn viết phóng to lên màn hình, tô sáng những tiếng dễ viết sai và mở bản đọc mẫu để HS…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài tập phân biệt s/x và v/d, GV mở bài tập tương tác: máy hiện từ còn thiếu chữ, HS chọn chữ đúng rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -5196,7 +5301,12 @@
           <t>178</t>
         </is>
       </c>
-      <c r="H124" s="4" t="inlineStr"/>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nghe – viết bài “Ngày như thế nào là đẹp?”, GV chiếu đoạn viết phóng to lên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài tập phân biệt r/d/gi và dấu hỏi, dấu ngã, GV mở bài tập tương tác: máy hiện từ còn thiếu, HS chọn chữ hoặc dấu thanh đúng rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -5455,7 +5565,9 @@
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>QPAN: Bồi dưỡng tình yêu quê hương, đất nước; giới thiệu truyền thống chống giặc ngoại xâm, gương dũng cảm của thiếu niên, nhi đồng và Bà mẹ Việt Nam anh hùng.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nghe – viết bài “Bản em”, GV chiếu đoạn viết phóng to lên màn hình, tô sáng những tiếng dễ viết sai và mở bản đọc mẫu để HS nghe rõ…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài tập phân biệt ch/tr và ươc/ươt, GV mở bài tập tương tác: máy hiện từ còn thiếu, HS chọn chữ hoặc vần đúng rồi bấm kiểm tra
+QPAN: Bồi dưỡng tình yêu quê hương, đất nước; giới thiệu truyền thống chống giặc ngoại xâm, gương dũng cảm của thiếu niên, nhi đồng và Bà mẹ Việt Nam anh hùng.</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5761,12 @@
           <t>199</t>
         </is>
       </c>
-      <c r="H136" s="4" t="inlineStr"/>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nghe – viết bài “Chợ Hòn Gai”, GV mở bản đồ số của cơ quan Nhà nước chỉ vị trí Hòn Gai cho HS biết địa danh trong bài nằm ở…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài tập viết hoa tên riêng địa lí, GV mở bài tập tương tác: máy hiện câu có tên riêng viết thường, HS sửa lại cho đúng rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -5844,7 +5961,12 @@
           <t>206</t>
         </is>
       </c>
-      <c r="H141" s="4" t="inlineStr"/>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nghe – viết bài “Nhà rông”, GV chiếu ảnh nhà rông Tây Nguyên phóng to cùng đoạn viết
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài tập phân biệt s/x và dấu hỏi, dấu ngã, GV mở bài tập tương tác: máy hiện từ còn thiếu, HS chọn chữ hoặc dấu thanh đúng rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -6036,7 +6158,12 @@
           <t>213</t>
         </is>
       </c>
-      <c r="H146" s="4" t="inlineStr"/>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nghe – viết bài “Hai Bà Trưng”, GV chiếu đoạn viết phóng to lên màn hình, tô sáng tên riêng cần viết hoa và mở bản đọc mẫu để HS nghe…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài tập phân biệt ch/tr và ai/ay, GV mở bài tập tương tác: máy hiện từ còn thiếu, HS chọn chữ hoặc vần đúng rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -6229,7 +6356,12 @@
           <t>220</t>
         </is>
       </c>
-      <c r="H151" s="4" t="inlineStr"/>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nghe – viết bài “Ngọn lửa Ô-lim-pích”, GV chiếu đoạn viết phóng to lên màn hình, tô sáng các tên riêng nước ngoài có dấu gạch nối và mở bản đọc…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài tập viết hoa tên riêng nước ngoài, GV mở bài tập tương tác: máy hiện tên riêng viết thường hoặc thiếu gạch nối, HS sửa lại rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -6420,7 +6552,12 @@
           <t>227</t>
         </is>
       </c>
-      <c r="H156" s="4" t="inlineStr"/>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nghe – viết bài “Em nghĩ về Trái Đất”, GV chiếu bài thơ phóng to lên màn hình cùng ảnh Trái Đất nhìn từ vũ trụ
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài tập phân biệt r/d/gi và dấu hỏi, dấu ngã, GV mở bài tập tương tác: máy hiện từ còn thiếu, HS chọn chữ hoặc dấu thanh đúng rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -6613,7 +6750,12 @@
           <t>234</t>
         </is>
       </c>
-      <c r="H161" s="4" t="inlineStr"/>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nghe – viết bài “Bác sĩ Y-éc-xanh”, GV chiếu đoạn viết phóng to lên màn hình, tô sáng tên riêng nước ngoài có dấu gạch nối và mở bản đọc mẫu…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài tập viết hoa tên riêng nước ngoài, GV mở bài tập tương tác: máy hiện tên riêng viết thường hoặc thiếu gạch nối, HS sửa lại rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -10635,7 +10777,8 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở chủ đề “Tự sắp xếp đồ dùng ngăn nắp”, GV chiếu cặp ảnh một góc học tập bừa bộn.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở chủ đề “Tự sắp xếp đồ dùng ngăn nắp”, GV chiếu cặp ảnh một góc học tập bừa bộn và một góc được phân loại theo nhóm
+Năng lực số Miền 3 (Cơ bản, bậc 1): HS sắp xếp lại cặp sách hoặc ngăn bàn, GV chụp ảnh trước và sau rồi chiếu lên màn hình; các em nhìn hai ảnh cạnh nhau nên thấy rõ kết quả việc mình…</t>
         </is>
       </c>
     </row>
@@ -10737,7 +10880,8 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>NLS-ST (Cơ bản 1): Ở chủ đề “Góc học tập đáng yêu”, HS vẽ hoặc làm mô hình góc học tập mơ ước; GV chụp ảnh.</t>
+          <t>Năng lực số Miền 3 (Cơ bản, bậc 1): Ở chủ đề “Góc học tập đáng yêu”, HS vẽ hoặc làm mô hình góc học tập mơ ước; GV chụp ảnh sản phẩm rồi chiếu thành trang trưng bày để mỗi em giới…
+Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu vài ảnh góc học tập có ánh sáng tốt và góc thiếu sáng, bàn ghế đúng và sai tầm; HS chỉ ra góc nào ngồi học đỡ mỏi</t>
         </is>
       </c>
     </row>
@@ -10840,7 +10984,8 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Khám phá chủ đề “Nhà là tổ ấm”, GV chiếu bộ ảnh các góc quen thuộc trong nhà.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá chủ đề “Nhà là tổ ấm”, GV chiếu bộ ảnh các góc quen thuộc trong nhà: góc học tập gọn gàng và bừa bộn
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở hoạt động Chia sẻ về góc em thích trong nhà, GV chiếu bảng chung có các cột “Góc em thích – Việc em làm”</t>
         </is>
       </c>
     </row>
@@ -10942,7 +11087,8 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Ở hoạt động Luyện tập, GV chiếu bảng chung “Dụng cụ – Việc dùng để làm – Lưu ý khi dùng”.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Chia sẻ về dụng cụ dọn vệ sinh của chủ đề “Nhà sạch thì mát”, GV chiếu ảnh chụp gần chổi, cây lau nhà, khăn lau
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV chiếu bảng chung “Dụng cụ – Việc dùng để làm – Lưu ý khi dùng”; các nhóm lần lượt lên điền để cả lớp nhìn chung một bảng</t>
         </is>
       </c>
     </row>
@@ -11044,7 +11190,8 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Khám phá chủ đề “Đồ dùng của người thân”, GV chiếu bộ ảnh những đồ dùng quen thuộc của.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá chủ đề “Đồ dùng của người thân”, GV chiếu bộ ảnh những đồ dùng quen thuộc của ông bà, bố mẹ như kính lão, chiếc chổi, hộp kim chỉ
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở hoạt động Chia sẻ, GV chiếu bảng chung “Người thân – Đồ dùng – Việc em làm để giữ gìn”; các nhóm lần lượt lên điền để cả lớp nhìn chung một bảng</t>
         </is>
       </c>
     </row>
@@ -11147,7 +11294,8 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>NLS-ST (Cơ bản 1): Ở hoạt động Viết lá thư tri ân, GV chiếu mẫu bưu thiếp trên máy tính lớp.</t>
+          <t>Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Viết lá thư tri ân, GV chiếu mẫu bưu thiếp trên máy tính lớp, cùng HS chọn hình nền, gõ thử lời chúc và chỉnh cỡ chữ cho dễ đọc
+Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu mẫu phong bì thư đã ghi đủ nơi gửi, nơi nhận, phóng to từng ô để HS biết viết gì vào đâu</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11606,8 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Khám phá chủ đề “Bếp nhà em”, GV chiếu bộ ảnh gian bếp.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá chủ đề “Bếp nhà em”, GV chiếu bộ ảnh gian bếp có nguy cơ mất an toàn: nồi quai hướng ra ngoài, dao để mép bàn
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác “Nếu… thì…”: máy hiện tình huống trong bếp, HS chọn cách xử lí an toàn rồi bấm kiểm tra</t>
         </is>
       </c>
     </row>
@@ -11557,7 +11706,8 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác sắp xếp các bước rửa tay trước khi ăn.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá chủ đề “Ăn sạch”, GV chiếu bộ ảnh so sánh: rau đã rửa và rau còn đất, thức ăn đậy lồng bàn và thức ăn để hở có ruồi
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác sắp xếp các bước rửa tay trước khi ăn: HS kéo các bước vào đúng thứ tự rồi bấm kiểm tra</t>
         </is>
       </c>
     </row>
@@ -11655,7 +11805,8 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Khám phá chủ đề “Bên mâm cơm”, GV chiếu bộ ảnh các cách ứng xử trong bữa ăn.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá chủ đề “Bên mâm cơm”, GV chiếu bộ ảnh các cách ứng xử trong bữa ăn: mời người lớn trước, dùng thìa chung để lấy thức ăn
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bảng chung “Quy tắc ứng xử bên mâm cơm”; các nhóm lần lượt lên ghi một quy tắc của nhóm mình để cả lớp nhìn chung một…</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11906,8 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở hoạt động Luyện tập, GV chiếu tình huống đi ăn.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá chủ đề “Ăn uống ngoài hàng quán”, GV chiếu bộ ảnh so sánh quán ăn sạch sẽ có che đậy thức ăn với quán bày thức ăn ngoài trời…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV chiếu tình huống đi ăn cùng gia đình; HS chọn việc nên làm là rửa tay trước khi ăn, chọn món nấu chín, không dùng chung cốc</t>
         </is>
       </c>
     </row>
@@ -11966,7 +12118,8 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Ở hoạt động Luyện tập, GV mở bảng chung “Món đồ – Mùa cần – Người có thể nhận”.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá chủ đề “Mùa đông ấm, mùa hè vui”, GV chiếu ảnh các món đồ có thể chia sẻ theo mùa: áo ấm, chăn, quạt, sách vở
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bảng chung “Món đồ – Mùa cần – Người có thể nhận”; các nhóm lên điền để cả lớp nhìn chung một bảng rồi thống nhất kế…</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12218,8 @@
       <c r="H83" s="4" t="inlineStr">
         <is>
           <t>KNS: Biết chia sẻ, yêu thương đặc biệt với những người khuyết tật giúp họ vơi đi vất vả cũng là giúp mình thêm vui vẻ, hạnh phúc
-NLS-KT (Cơ bản 1): Ở hoạt động Khám phá chủ đề “Giúp đỡ người khuyết tật”, GV chiếu ảnh.</t>
+Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá chủ đề “Giúp đỡ người khuyết tật”, GV chiếu ảnh và đoạn phim ngắn về bảng chữ cái ngón tay, chữ nổi Brai, xe lăn, gậy dò đường
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bảng chung “Khó khăn của bạn – Việc em giúp được”; các nhóm lên điền như nói chậm rõ để bạn đọc khẩu hình, nhường lối đi</t>
         </is>
       </c>
     </row>
@@ -12796,7 +12950,8 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Khám phá chủ đề “An toàn là bạn”, GV chiếu ảnh các dụng cụ lao động quen thuộc kèm.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá chủ đề “An toàn là bạn”, GV chiếu ảnh các dụng cụ lao động quen thuộc kèm hình cảnh báo, phóng to phần lưỡi
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: máy hiện tình huống dùng dụng cụ chưa an toàn, HS chọn cách sửa rồi bấm kiểm tra và giải thích
 KNS: KN ứng phó với tình huống nguy hiểm và tìm kiếm sự trợ giúp.</t>
         </is>
       </c>
@@ -13169,7 +13324,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần khám phá bài “Bài 3. Tìm thành phần trong phép cộng, phép trừ (Tiết 1)”, GV chiếu hình ảnh động bài toán táo xanh, táo đỏ trong SGK
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần luyện tập, GV chiếu bài tập tương tác dạng ? + 5 = 12 hoặc 7 + ? = 15</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -13876,7 +14036,8 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Mở bài tập tương tác điền số vào ô trống của phép nhân, phép chia; máy chấm ngay nên HS biết mình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài tìm thành phần trong phép nhân, phép chia, GV chiếu sơ đồ phép tính có một ô trống và bấm cho phần đã biết sáng lên
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác điền số vào ô trống của phép nhân, phép chia; máy chấm ngay nên HS biết mình chọn phép tính ngược đúng chưa
 KNS: KN chi tiêu hợp lí: tính toán khi mua bán, biết tiết kiệm.</t>
         </is>
       </c>
@@ -13937,7 +14098,9 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>STEM: Trải nghiệm cùng một phần mấy (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài “Một phần mấy”, GV dùng hình động trên máy: chia một hình tròn, một băng giấy thành hai, thành bốn phần bằng nhau rồi tô màu một phần
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV chiếu các hình chia phần không bằng nhau xen lẫn hình chia đúng, cho HS chọn hình đã tô một phần tư; máy báo đúng
+STEM: Trải nghiệm cùng một phần mấy (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14324,8 @@
       <c r="H39" s="4" t="inlineStr">
         <is>
           <t>Gồm cả Bài 19 (Tổ CM đối chiếu mục lục SGK)
-NLS-GQVĐ (Cơ bản 1): Chiếu nhiều hình có góc khác nhau cho HS chọn góc vuông trước khi kiểm tra bằng ê ke thật.</t>
+Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài “Góc, góc vuông, góc không vuông”, GV dùng hình động trên máy: kéo một cạnh cho góc mở rộng dần và bấm hiện ê ke áp vào góc
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV chiếu nhiều hình có góc khác nhau cho HS chọn góc vuông trước khi kiểm tra bằng ê ke thật; máy báo đúng</t>
         </is>
       </c>
     </row>
@@ -14193,7 +14357,12 @@
           <t>37</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài về hình tam giác, tứ giác, hình chữ nhật và hình vuông, GV chiếu hình trên máy rồi xoay, phóng to thu nhỏ; HS nhận ra hình vẫn giữ nguyên số cạnh
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác kéo mỗi hình về đúng nhóm và đánh dấu góc vuông của hình chữ nhật, hình vuông; máy báo đúng</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -14275,7 +14444,12 @@
           <t>40</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài “Thực hành vẽ góc vuông, vẽ đường tròn , hình vuông, hình chữ nhật và vẽ trang trí”, GV dùng phần mềm hình học động chiếu lên màn hình: kéo một đỉnh…
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV cho HS dự đoán trước rồi mới kéo hình để kiểm tra: “Nếu chiều dài tăng gấp đôi thì chu vi thay đổi thế nào?”. HS nói dự đoán, GV thao tác</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -14465,7 +14639,8 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Mở bài tập tương tác đặt tính.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở tiết luyện tập nhân số có hai chữ số với số có một chữ số, GV chiếu phép nhân đặt tính trên màn hình rồi bấm hiện dần từng bước nhân hàng đơn…
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác đặt tính rồi tính, máy báo đúng, sai ngay và chỉ chỗ sai; HS nhận ra mình quên cộng phần nhớ hay viết lệch cột</t>
         </is>
       </c>
     </row>
@@ -14497,7 +14672,12 @@
           <t>47</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài “Gấp một số lên một số lần”, GV dùng hình động trên máy: bấm cho một nhóm đồ vật nhân lên thành hai lần, ba lần và hiện phép tính bên cạnh
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV chiếu các bài toán ngắn có từ gấp lên và thêm vào xen kẽ nhau, cho HS chọn phép tính đúng; máy báo đúng</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -14553,7 +14733,12 @@
           <t>49</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài phép chia hết và phép chia có dư, GV dùng hình động chia đều số viên phấn vào các hộp; khi còn viên lẻ không xếp được nữa
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác cho HS chia và ghi thương, ghi số dư; máy báo đúng, sai ngay nên các em nhận ra mình ghi số dư lớn hơn số chia là…</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -14611,7 +14796,8 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở bài chia số có hai chữ số cho số có một chữ số, GV chiếu phép chia đặt tính trên màn hình.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài chia số có hai chữ số cho số có một chữ số, GV chiếu phép chia đặt tính trên màn hình rồi bấm hiện dần từng bước chia hàng chục, hạ số
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác đặt tính rồi tính, máy báo đúng, sai ngay và chỉ chỗ sai; HS nhận ra mình quên hạ số hay viết thương lệch cột</t>
         </is>
       </c>
     </row>
@@ -14695,7 +14881,12 @@
           <t>54</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài “Giảm một số đi một số lần”, GV dùng hình động trên máy: bấm cho một nhóm đồ vật bớt đi còn một nửa
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV chiếu xen kẽ các bài toán có từ giảm đi và bớt đi, cho HS chọn phép tính đúng; máy báo đúng</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -14753,7 +14944,8 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Chiếu một bài giải mẫu rồi ẩn bước thứ nhất.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài toán giải bằng hai bước tính, GV chiếu sơ đồ đoạn thẳng trên máy và bấm hiện dần từng dữ kiện
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV chiếu một bài giải mẫu rồi ẩn bước thứ nhất; HS nói bước còn thiếu, khi các em nêu sai thứ tự thì GV bấm hiện lại sơ đồ để cả lớp thấy…
 KNS: KN chi tiêu hợp lí: tính toán khi mua bán, biết tiết kiệm.</t>
         </is>
       </c>
@@ -15171,7 +15363,12 @@
           <t>69</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài nhân số có ba chữ số với số có một chữ số, GV chiếu phép nhân đặt tính trên màn hình rồi bấm hiện dần từng bước nhân hàng đơn vị
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác đặt tính rồi tính, máy báo đúng, sai ngay và chỉ chỗ sai; HS nhận ra mình quên cộng phần nhớ hay viết lệch cột</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -15229,7 +15426,8 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Khám phá bài “Chia số có ba chữ số cho số có một chữ số”, GV chiếu hình vẽ.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Chia số có ba chữ số cho số có một chữ số”, GV chiếu hình vẽ và lời thoại của Rô-bốt, Mai, Việt lên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác đặt tính rồi tính: HS làm ra nháp trước, sau đó nhập kết quả vào máy</t>
         </is>
       </c>
     </row>
@@ -15315,7 +15513,9 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>Gồm cả Bài 39–41 (Tổ CM đối chiếu mục lục SGK)</t>
+          <t>Gồm cả Bài 39–41 (Tổ CM đối chiếu mục lục SGK)
+Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động làm quen với biểu thức của bài “Biểu thức số. Tính giá trị của biểu thức số”, GV chiếu các biểu thức lên màn hình và tô màu theo thứ tự…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác nối biểu thức với giá trị đúng: HS tính ra nháp rồi kéo nối trên màn hình</t>
         </is>
       </c>
     </row>
@@ -15427,7 +15627,8 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: máy hiện hai số, HS chọn phép tính tìm số lớn.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “So sánh số lớn gấp mấy lần số bé”, GV chiếu sơ đồ đoạn thẳng lên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: máy hiện hai số, HS chọn phép tính tìm số lớn gấp mấy lần số bé rồi bấm kiểm tra</t>
         </is>
       </c>
     </row>
@@ -15826,7 +16027,8 @@
       <c r="H94" s="4" t="inlineStr">
         <is>
           <t>Gồm cả Bài 45 (Tổ CM đối chiếu mục lục SGK)
-NLS-KT (Cơ bản 1): Ở hoạt động Khám phá bài “Các số có bốn chữ số. Số 10 000”, GV chiếu bảng các hàng nghìn, trăm.</t>
+Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Các số có bốn chữ số. Số 10 000”, GV chiếu bảng các hàng nghìn, trăm, chục, đơn vị lên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: máy hiện số, HS kéo các chữ số vào đúng cột hàng rồi bấm kiểm tra</t>
         </is>
       </c>
     </row>
@@ -15910,7 +16112,12 @@
           <t>94</t>
         </is>
       </c>
-      <c r="H97" s="4" t="inlineStr"/>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài “So sánh các số trong phạm vi 10 000”, GV chiếu bảng hàng động trên máy: thêm hoặc bớt một khối ở hàng đơn vị, hàng chục, hàng trăm
+Năng lực số Miền 5 (Cơ bản, bậc 1): Với chữ số La Mã, GV chiếu ảnh mặt đồng hồ, bìa sách, biển số nhà, số ghi thế kỉ trên bảng di tích – những chỗ chữ số La Mã còn được dùng…</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -16508,7 +16715,8 @@
       <c r="H116" s="4" t="inlineStr">
         <is>
           <t>Gồm cả Bài 55 (Tổ CM đối chiếu mục lục SGK)
-NLS-KT (Cơ bản 1): Ở hoạt động Khám phá bài “Phép cộng trong phạm vi 10 000”, GV chiếu phép cộng đặt tính dọc lên màn.</t>
+Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Phép cộng trong phạm vi 10 000”, GV chiếu phép cộng đặt tính dọc lên màn hình và cho hiện dần từng hàng đơn vị, chục, trăm
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS đặt tính và tính ra vở trước rồi nhập kết quả; khi máy báo sai</t>
         </is>
       </c>
     </row>
@@ -16570,7 +16778,12 @@
           <t>115</t>
         </is>
       </c>
-      <c r="H118" s="4" t="inlineStr"/>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Phép trừ trong phạm vi 10 000”, GV chiếu phép trừ đặt tính dọc lên màn hình và cho hiện dần từng hàng
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS tính ra vở trước rồi nhập kết quả; khi máy báo sai</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -16632,7 +16845,8 @@
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Nhân số có bốn chữ số với số có một chữ số”, GV chiếu phép nhân đặt tính dọc lên màn hình và cho hiện dần từng lượt…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS đặt tính và tính ra vở trước rồi nhập kết quả; khi máy báo sai</t>
         </is>
       </c>
     </row>
@@ -16716,7 +16930,12 @@
           <t>120</t>
         </is>
       </c>
-      <c r="H123" s="4" t="inlineStr"/>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Chia số có bốn chữ số cho số có một chữ số”, GV chiếu phép chia đặt tính lên màn hình và cho hiện dần từng lượt chia
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS tính ra vở trước rồi nhập kết quả; khi máy báo sai</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -17210,7 +17429,8 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Phép cộng trong phạm vi 100 000”, GV chiếu phép cộng đặt tính dọc lên màn hình và cho hiện dần từng hàng cùng số nhớ
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS đặt tính và tính ra vở trước rồi nhập kết quả; khi máy báo sai</t>
         </is>
       </c>
     </row>
@@ -17268,7 +17488,12 @@
           <t>138</t>
         </is>
       </c>
-      <c r="H141" s="4" t="inlineStr"/>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Phép trừ trong phạm vi 100 000”, GV chiếu phép trừ đặt tính dọc lên màn hình và cho hiện dần từng hàng
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS tính ra vở trước rồi nhập kết quả; khi máy báo sai</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -17647,7 +17872,12 @@
           <t>150</t>
         </is>
       </c>
-      <c r="H153" s="4" t="inlineStr"/>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Nhân số có năm chữ số với số có một chữ số”, GV chiếu phép nhân đặt tính dọc lên màn hình và cho hiện dần từng lượt…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS đặt tính và tính ra vở trước rồi nhập kết quả; khi máy báo sai</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -17731,7 +17961,8 @@
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Khám phá bài “Chia số có năm chữ số cho số có một chữ số”.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Chia số có năm chữ số cho số có một chữ số”, GV chiếu phép chia đặt tính lên màn hình và cho hiện dần từng lượt chia
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS tính ra vở trước rồi nhập kết quả; khi máy báo sai</t>
         </is>
       </c>
     </row>
@@ -18692,7 +18923,8 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở bài “Quan tâm hàng xóm láng giềng”, GV chiếu bộ ảnh việc làm quen thuộc trong xóm như trông giúp nhà.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài “Quan tâm hàng xóm láng giềng”, GV chiếu bộ ảnh việc làm quen thuộc trong xóm như trông giúp nhà bên, đưa cụ già qua đường, cùng dọn ngõ sau mưa
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV chiếu các tình huống trên màn hình và cho HS chọn cách ứng xử phù hợp khi nhà hàng xóm có việc, khi em ở nhà một mình mà người lạ gọi cửa</t>
         </is>
       </c>
     </row>
@@ -18932,7 +19164,8 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở bài “Giữ lời hứa”, GV chiếu các đoạn phim tình huống ngắn về việc hứa.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài “Giữ lời hứa”, GV chiếu các đoạn phim tình huống ngắn về việc hứa rồi quên, hứa rồi thực hiện
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV gõ lên màn hình những lời hứa mà HS muốn thực hiện trong tuần, thành bảng chung của lớp; cả lớp cùng đọc lại</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19282,8 @@
       <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Bài 6 học vắt sang đầu HKII — tổ chuyên môn chủ động bố trí.
-NLS-GQVĐ (Cơ bản 1): Ở hoạt động Tìm hiểu ý nghĩa, GV chiếu hai tình huống.</t>
+Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Tìm hiểu biểu hiện của bài “Tích cực hoàn thành nhiệm vụ”, GV chiếu tranh truyện “Tham gia việc lớp” phóng to theo từng đoạn
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Tìm hiểu ý nghĩa, GV chiếu hai tình huống cùng một công việc: một bên làm xong đúng hạn, một bên bỏ dở</t>
         </is>
       </c>
     </row>
@@ -19855,7 +20089,8 @@
         <is>
           <t>GDMT: Có ý thức giữ gìn vệ sinh, bảo vệ môi trường xung quanh sạch đẹp - Biết làm một số việc vừa sức để giữ gìn môi trường xung quanh: vứt rác đúng nơi quy định, sắp xếp đồ dùng trong nhà gọn gàng, sạch sẽ.
 GDĐP: Em đã làm gì để cho đường làng ngõ xóm nơi em ở sạch sẽ.
-NLS-KT (Cơ bản 1): Ở bài “Vệ sinh xung quanh nhà”, GV chiếu bộ ảnh hai khu vực quanh nhà.
+Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài “Vệ sinh xung quanh nhà”, GV chiếu bộ ảnh hai khu vực quanh nhà: một nơi sạch sẽ, một nơi có rác ứ đọng, vũng nước tù; HS quan sát
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV chiếu từng tình huống quanh nhà và cho HS chọn cách xử lí trên màn hình như đổ nước đọng trong lốp xe, thu gom rác vào thùng có nắp; máy báo đúng
 KNS: KN tự chăm sóc bản thân: giữ vệ sinh, ăn uống, nghỉ ngơi điều độ.</t>
         </is>
       </c>
@@ -21003,7 +21238,8 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Khám phá bài “Chăm sóc và bảo vệ cơ quan tiêu hoá”, GV chiếu bộ ảnh thức ăn.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Chăm sóc và bảo vệ cơ quan tiêu hoá”, GV chiếu bộ ảnh thức ăn để hở có ruồi đậu, tay chưa rửa cầm thức ăn, nước lã
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác phân loại: máy hiện các việc làm, HS chọn việc giúp bảo vệ cơ quan tiêu hoá hay việc có hại rồi bấm…
 QPAN: Giới thiệu truyền thống chống giặc ngoại xâm, gương dũng cảm của thiếu niên, nhi đồng và Bà mẹ Việt Nam anh hùng; kể việc làm của các chú bộ đội, công an giúp dân ở địa phương.</t>
         </is>
       </c>
@@ -21129,7 +21365,8 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Khám phá bài “Chăm sóc và bảo vệ cơ quan tuần hoàn”, GV chiếu ảnh so sánh lối sống.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Chăm sóc và bảo vệ cơ quan tuần hoàn”, GV chiếu ảnh so sánh lối sống có lợi và có hại cho tim: tập thể dục đều
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV chiếu tình huống bạn nhỏ hay tức ngực, tim đập nhanh sau khi chạy nhiều; HS chọn cách xử lí là nghỉ ngơi, uống nước
 QPAN: Giới thiệu truyền thống chống giặc ngoại xâm, gương dũng cảm của thiếu niên, nhi đồng và Bà mẹ Việt Nam anh hùng; kể việc làm của các chú bộ đội, công an giúp dân ở địa phương.</t>
         </is>
       </c>
@@ -22002,7 +22239,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Mở đầu bài “Starter — A. Numbers”, GV chiếu video bài hát Hello song và đoạn video đếm số, yêu cầu HS quan sát
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần luyện tập, GV tổ chức trò chơi nghe–chọn tranh trên máy chiếu: máy đọc một số, HS chọn tranh có số lượng đồ vật tương ứng hoặc chọn từ đúng như six</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -22032,7 +22274,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần trình bày bài “Starter — B. The Alphabet”, GV chiếu video bài hát bảng chữ cái và bản ghi âm người bản ngữ đọc từng chữ cái; HS nghe
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần luyện tập đánh vần tên, GV dùng điện thoại ghi âm một vài HS đánh vần tên mình (M-A-I), phát lại qua loa để cả lớp nghe</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -22062,7 +22309,12 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Khởi động bài “Starter — C. Fun Time”, GV chiếu video bài hát đếm số Let’s count 1-10, HS vừa hát vừa giơ ngón tay theo số nghe được
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần thực hành, GV tổ chức trò chơi Bingo bằng bài tập tương tác trên máy chiếu: máy đọc ngẫu nhiên số hoặc chữ cái</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -22163,7 +22415,9 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần trình bày bài “Unit 1 — Hello — Lesson 2 (Asking how someone is) – Tiết 1”, GV chiếu tranh hai tình huống kèm bản ghi âm người bản ngữ: Hi.
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV hỏi HS có thể hỏi thăm bạn bằng cách nào (gặp trực tiếp, gọi điện, nhắn tin) và chiếu hình minh hoạ từng cách
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -22231,7 +22485,8 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở phần nghe của bài Unit 1 Hello, GV mở tệp ghi âm câu chào.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần nghe của bài Unit 1 Hello, GV mở tệp ghi âm câu chào và câu đáp cho HS nghe hai lượt, lần hai dừng sau từng câu
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt hỏi đáp chào hỏi của vài cặp HS rồi mở lại cho cả lớp nghe; các em so với giọng mẫu để nhận ra chỗ phát âm chưa đúng
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -22300,7 +22555,9 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Vào bài Unit 2 Our names, GV chiếu tranh và mở tệp ghi âm mẫu câu hỏi tên, trả lời tên; HS nghe rồi chỉ vào đúng nhân vật trên màn hình
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV chiếu bảng tên của lớp lên màn hình, mỗi em lần lượt hỏi tên bạn và gõ hoặc đọc để thầy cô ghi tên bạn vào đúng ô
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -22368,7 +22625,8 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Chiếu bảng tên của lớp lên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài Unit 2 Our names phần đánh vần tên, GV chiếu bảng chữ cái tiếng Anh có kèm âm đọc: bấm vào chữ nào thì máy phát âm chữ đó
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV chiếu bảng tên của lớp lên màn hình; từng cặp HS hỏi tên bạn và đánh vần tên mình cho bạn nghe
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -22437,7 +22695,9 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần nghe của bài Unit 2 Our names, GV mở tệp ghi âm hai lượt: lượt một nghe lấy ý chung, lượt hai dừng sau từng câu; HS nhìn tranh trên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối câu hỏi với câu trả lời và điền chữ cái còn thiếu trong tên; máy chấm ngay nên HS biết mình nghe sót chữ nào
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -22505,7 +22765,8 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Vào bài Unit 3 Our friends, GV chiếu tranh các nhân vật kèm tệp ghi âm mẫu câu giới thiệu bạn.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Vào bài Unit 3 Our friends, GV chiếu tranh các nhân vật kèm tệp ghi âm mẫu câu giới thiệu bạn; HS nghe hai lượt
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV chiếu bảng ba cột tên bạn, tuổi và một điều bạn thích; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô điền vào bảng
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -22574,7 +22835,9 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài Unit 3 phần nói về bạn bè, GV mở bài tập tương tác ghép câu hỏi với câu trả lời và chọn từ đúng để tả bạn
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt hỏi đáp về bạn của một vài cặp rồi mở cho cả lớp nghe; các em nhận xét theo tiêu chí nói đủ câu, phát âm rõ
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -22642,7 +22905,8 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Mở bài tập tương tác nối câu hỏi với câu trả lời và điền từ còn thiếu trong câu giới thiệu bạn.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần nghe của bài Unit 3 Our friends, GV mở tệp ghi âm hai lượt, lượt sau dừng từng câu; HS nhìn tranh trên màn hình, chỉ đúng bạn đang được giới thiệu
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối câu hỏi với câu trả lời và điền từ còn thiếu trong câu giới thiệu bạn; máy chấm ngay nên HS biết mình nghe sót chỗ nào
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -22711,7 +22975,9 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Vào bài Unit 4 Our bodies, GV chiếu hình người có chú thích các bộ phận cơ thể kèm tệp ghi âm; bấm vào bộ phận nào thì máy đọc từ đó
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV cho cả lớp chơi trò nghe hiệu lệnh trên màn hình rồi chỉ đúng bộ phận cơ thể theo cặp
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -22779,7 +23045,8 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở bài Unit 4 Our bodies phần tả cơ thể, GV mở bài hát về các bộ phận cơ thể rồi chiếu.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài Unit 4 Our bodies phần tả cơ thể, GV mở bài hát về các bộ phận cơ thể rồi chiếu tranh nhân vật kèm từ khoá
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nghe rồi chọn đúng nhân vật được tả và nối từ với bộ phận cơ thể; máy chấm ngay nên HS biết mình còn nhầm từ nào
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -22848,7 +23115,9 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần nghe của bài Unit 4 Our bodies, GV mở tệp ghi âm hai lượt, lượt sau dừng từng câu; HS nhìn tranh trên màn hình, chỉ đúng nhân vật được nhắc tới
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác điền từ còn thiếu vào câu tả người và nối câu với tranh; máy chấm ngay nên HS nhận ra mình nghe sót chỗ nào
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -22916,7 +23185,8 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Chiếu bảng khảo sát sở thích của lớp.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Vào bài Unit 5 My hobbies, GV chiếu bộ tranh sở thích kèm tệp ghi âm mẫu; HS nghe rồi nối tên sở thích với tranh
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV chiếu bảng khảo sát sở thích của lớp; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô đánh dấu vào bảng
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -22985,7 +23255,9 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài Unit 5 phần nói về sở thích mình yêu thích, GV mở bài tập tương tác nghe chọn tranh và ghép câu hỏi với câu trả lời
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt hỏi đáp của vài cặp rồi mở cho cả lớp nghe; các em nhận xét theo tiêu chí nói đủ câu, phát âm rõ, trả lời đúng nội dung
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -23053,7 +23325,8 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở phần nghe của bài Unit 5 My hobbies, GV mở tệp ghi âm hai lượt, lượt sau dừng từng câu.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần nghe của bài Unit 5 My hobbies, GV mở tệp ghi âm hai lượt, lượt sau dừng từng câu; HS nhìn tranh trên màn hình, chỉ đúng sở thích của nhân vật
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối câu hỏi với câu trả lời và điền từ còn thiếu vào câu nói về sở thích
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -23212,7 +23485,8 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Chiếu bảng ba cột tên phòng, vị trí và hoạt động thường diễn ra ở đó.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Vào bài Unit 6 Our school, GV chiếu sơ đồ trường mình có chú thích các phòng bằng tiếng Anh kèm tệp ghi âm; HS nghe rồi chỉ đúng phòng trên sơ đồ
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV chiếu bảng ba cột tên phòng, vị trí và hoạt động thường diễn ra ở đó; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô điền
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -23281,7 +23555,9 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài Unit 6 phần tả trường học, GV mở bài tập tương tác nghe chọn tranh và ghép từ chỉ nơi chốn với từ tả đặc điểm
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt hỏi đáp tả trường của vài cặp rồi mở cho cả lớp nghe; các em nhận xét theo tiêu chí nói đủ câu, phát âm rõ, dùng đúng từ tả
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -23349,7 +23625,8 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở phần nghe của bài Unit 6 Our school, GV mở tệp ghi âm hai lượt, lượt sau dừng từng câu.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần nghe của bài Unit 6 Our school, GV mở tệp ghi âm hai lượt, lượt sau dừng từng câu; HS nhìn tranh trên màn hình, chỉ đúng phòng học được nhắc tới
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối câu hỏi với câu trả lời và điền từ còn thiếu vào câu giới thiệu trường; máy chấm ngay nên HS biết mình nghe sót chỗ nào
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -23418,7 +23695,9 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 1): Vào bài Unit 7 Classroom instructions, GV chiếu các mệnh lệnh lớp học kèm hình minh hoạ và bản ghi âm; cả lớp nghe rồi làm theo hiệu lệnh trên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối mệnh lệnh với hình đúng và chọn câu phù hợp cho từng tình huống trong lớp; máy báo đúng
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -23486,7 +23765,8 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Ở bài Unit 7 phần nói lời đề nghị, GV chiếu các tình huống lớp học.
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 1): Ở bài Unit 7 phần nói lời đề nghị, GV chiếu các tình huống lớp học kèm mẫu câu đề nghị lịch sự và bản ghi âm; HS nghe rồi thực hành theo cặp
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối tình huống với câu đề nghị phù hợp; máy báo đúng, sai ngay nên HS nhận ra câu nào lịch sự
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -23555,7 +23835,9 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần nghe của bài Unit 7 Classroom instructions, GV mở tệp ghi âm hai lượt, lượt sau dừng từng câu; HS nhìn tranh trên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối câu với tranh và điền từ còn thiếu vào mệnh lệnh; máy chấm ngay nên HS biết mình nghe sót chỗ nào
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -23623,7 +23905,8 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Vào bài Unit 8 My school things, GV chiếu bộ tranh đồ dùng học tập.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Vào bài Unit 8 My school things, GV chiếu bộ tranh đồ dùng học tập kèm tệp ghi âm mẫu; HS nghe rồi nối tên đồ dùng với tranh
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV chiếu bảng đồ dùng học tập của lớp; từng cặp HS hỏi đáp bằng tiếng Anh xem bạn có những gì trong cặp rồi đọc để thầy cô đánh dấu
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -23692,7 +23975,9 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài Unit 8 phần hỏi số lượng, GV chiếu tranh có nhiều đồ dùng kèm tệp ghi âm; HS nghe rồi đếm và chỉ đúng số lượng trên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nghe rồi chọn số đúng và ghép câu hỏi với câu trả lời; máy chấm ngay nên HS nhận ra mình còn nhầm số nào
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -23760,7 +24045,8 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Mở bài tập tương tác nối câu hỏi với câu trả lời và điền từ còn thiếu; máy chấm ngay nên.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần nghe của bài Unit 8 My school things, GV mở tệp ghi âm hai lượt, lượt sau dừng từng câu; HS nhìn tranh trên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối câu hỏi với câu trả lời và điền từ còn thiếu; máy chấm ngay nên HS biết mình nghe sót chỗ nào
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -23829,7 +24115,9 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Vào bài Unit 9 Colours, GV chiếu bảng màu và các đồ vật nhiều màu kèm tệp ghi âm; HS nghe rồi chỉ đúng màu trên màn hình
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV chiếu bảng khảo sát màu yêu thích của lớp; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô đánh dấu
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -23897,7 +24185,8 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Look, listen and repeat của Unit 9 “Colours”, GV chiếu tranh các đồ vật.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Look, listen and repeat của Unit 9 “Colours”, GV chiếu tranh các đồ vật kèm màu sắc lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Lucky number, GV mở trò chơi trên máy chiếu: HS chọn số, máy hiện câu hỏi về màu của đồ vật, HS trả lời rồi bấm kiểm tra
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -23966,7 +24255,9 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and number của Unit 9 “Colours”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS nối tranh với số thứ tự
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Find and circle the words, GV chiếu bảng chữ cái lên màn hình, HS lên khoanh các từ chỉ màu tìm được
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -24034,7 +24325,8 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở phần Warm-up trò chơi Jigsaw puzzle, GV chiếu các mảnh tranh rời trên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Look, listen and repeat của Unit 10 “Break time activities”, GV chiếu tranh các hoạt động giờ ra chơi lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Jigsaw puzzle, GV chiếu các mảnh tranh rời trên màn hình; bốn nhóm đoán và ghép thành bức tranh giờ ra chơi
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -24103,7 +24395,9 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and repeat của Unit 10 “Break time activities”, GV chiếu tranh lên màn hình và mở bản nghe mẫu về việc bạn thích làm giờ ra chơi
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Act and Guess, GV chiếu từ gợi ý riêng cho bạn lên bảng nhìn, đội còn lại đoán hoạt động qua động tác
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -24171,7 +24465,8 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Listen and repeat của Unit 10, GV mở bản nghe mẫu hai âm f và v trong football và volleyball, cho nghe chậm.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and repeat của Unit 10, GV mở bản nghe mẫu hai âm f và v trong football và volleyball
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Find and circle the words, GV chiếu bảng chữ cái lên màn hình, HS lên khoanh các từ về hoạt động giờ ra chơi tìm được
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -24390,7 +24685,8 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở phần Warm-up trò chơi Jigsaw puzzle, GV chiếu các mảnh tranh gia đình bị xáo trộn.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Look, listen and repeat của Unit 11 “My family”, GV chiếu tranh gia đình lên màn hình và mở bản nghe mẫu các từ chỉ thành viên trong gia đình
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Jigsaw puzzle, GV chiếu các mảnh tranh gia đình bị xáo trộn; bốn nhóm lên ghép thành bức tranh hoàn chỉnh
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -24459,7 +24755,9 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and repeat của Unit 11, GV chiếu tranh và mở bản nghe mẫu mẫu câu Who's this? – This is my…
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Pass the ball, GV mở nhạc và chiếu mẫu câu lên màn hình; khi nhạc dừng
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -24527,7 +24825,8 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Listen and repeat của Unit 11 “My family”, GV chiếu tranh gia đình và mở bản nghe mẫu, dừng sau mỗi câu.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and repeat của Unit 11 “My family”, GV chiếu tranh gia đình và mở bản nghe mẫu
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi What is missing, GV chiếu bộ thẻ từ lên màn hình rồi giấu đi một thẻ; các đội nhìn màn hình đoán thẻ nào biến mất
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -24596,7 +24895,9 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Look, listen and repeat của Unit 12 “Jobs”, GV chiếu tranh những người đang làm việc lên màn hình và mở bản nghe mẫu tên các nghề
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Jigsaw puzzle, GV chiếu các mảnh tranh nghề nghiệp bị xáo trộn; bốn nhóm lên ghép thành bức tranh hoàn chỉnh
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -24664,7 +24965,8 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Ở phần Warm-up trò chơi Pass the ball, GV mở nhạc.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Look, listen and repeat của Unit 12 “Jobs”, GV chiếu tranh những người đang làm việc và mở bản nghe mẫu mẫu câu What's his job? – He's a…
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Pass the ball, GV mở nhạc và chiếu mẫu câu lên màn hình; khi nhạc dừng, bạn cầm bóng nhìn mẫu câu để hỏi đáp với bạn bên cạnh
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -24733,7 +25035,9 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and number của Unit 12 “Jobs”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS nối tranh với số thứ tự
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Find and circle the words, GV chiếu bảng chữ cái lên màn hình, HS lên khoanh các từ chỉ nghề tìm được
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -24801,7 +25105,8 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Look, listen and repeat của Unit 13 “My house”, GV chiếu tranh ngôi nhà cắt ngang thấy rõ từng.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Look, listen and repeat của Unit 13 “My house”, GV chiếu tranh ngôi nhà cắt ngang thấy rõ từng phòng và mở bản nghe mẫu tên các phòng
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Jigsaw puzzle, GV chiếu các mảnh tranh ngôi nhà bị xáo trộn; bốn nhóm lên ghép thành bức tranh hoàn chỉnh
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -24870,7 +25175,9 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and repeat của Unit 13, GV chiếu tranh đồ vật đặt ở các vị trí khác nhau và mở bản nghe mẫu mẫu câu Where is it? – It's in
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần luyện tập, GV mở bài tập tương tác: máy hiện tranh, HS kéo đồ vật về đúng vị trí được nói trong câu rồi bấm kiểm tra
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -24938,7 +25245,8 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở phần Warm-up trò chơi Find and circle the words, GV chiếu bảng chữ cái lên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and number của Unit 13 “My house”, GV chiếu tranh các phòng lên màn hình và mở bản nghe
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Find and circle the words, GV chiếu bảng chữ cái lên màn hình, HS lên khoanh các từ về phòng và đồ vật trong nhà
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -25007,7 +25315,9 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Look, listen and repeat của Unit 14 “My bedroom”, GV chiếu tranh phòng ngủ có đủ đồ vật và mở bản nghe mẫu tên từng đồ
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Jigsaw puzzle, GV chiếu các mảnh tranh phòng ngủ bị xáo trộn; bốn nhóm lên ghép thành bức tranh hoàn chỉnh
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -25075,7 +25385,8 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Look, listen and repeat của Unit 14 “My bedroom”, GV chiếu tranh phòng ngủ.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Look, listen and repeat của Unit 14 “My bedroom”, GV chiếu tranh phòng ngủ có nhiều đồ vật và mở bản nghe mẫu mẫu câu How many…?
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Who says fast, GV chiếu thẻ đồ dùng kèm câu thiếu từ lên màn hình; các nhóm đoán nhanh từ còn thiếu
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -25144,7 +25455,9 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and number của Unit 14, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS nối tranh với số thứ tự
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Find and circle the words, GV chiếu bảng chữ cái lên màn hình, HS lên khoanh các từ về đồ vật trong phòng ngủ
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -25212,7 +25525,8 @@
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở phần Warm-up trò chơi Jigsaw puzzle, GV chiếu các mảnh tranh bàn ăn bị xáo trộn.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Look, listen and repeat của Unit 15 “At the dining table”, GV chiếu tranh bàn ăn có nhiều món và mở bản nghe mẫu tên món ăn, đồ uống
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Jigsaw puzzle, GV chiếu các mảnh tranh bàn ăn bị xáo trộn; bốn nhóm lên ghép thành bức tranh hoàn chỉnh
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -25281,7 +25595,9 @@
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and repeat của Unit 15, GV chiếu tranh và mở bản nghe mẫu mẫu câu Would you like…? – Yes, please / No, thanks
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Board Race, GV chiếu chủ đề đồ ăn, đồ uống lên màn hình; hai đội thay nhau viết từ
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -25349,7 +25665,8 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Listen and number của Unit 15 “At the dining table”, GV chiếu tranh món ăn lên màn hình và.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and number của Unit 15 “At the dining table”, GV chiếu tranh món ăn lên màn hình và mở bản nghe
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Find and circle the words, GV chiếu bảng chữ cái lên màn hình, HS lên khoanh các từ chỉ món ăn, đồ uống
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -25508,7 +25825,8 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở phần Warm-up trò chơi ghép tranh, GV chiếu các mảnh tranh con vật bị xáo trộn.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Look, listen and repeat của Unit 16 “My pets”, GV chiếu tranh các con vật nuôi lên màn hình và mở bản nghe mẫu tên con vật
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi ghép tranh, GV chiếu các mảnh tranh con vật bị xáo trộn; bốn nhóm lên ghép thành bức tranh hoàn chỉnh
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -25577,7 +25895,9 @@
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and repeat của Unit 16, GV chiếu tranh và mở bản nghe mẫu mẫu câu How many pets…?
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Guessing and Choosing, GV chiếu bốn bức tranh lên màn hình; HS chọn tranh và đặt câu hỏi để đoán
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -25645,7 +25965,8 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Listen and number của Unit 16 “My pets”, GV chiếu tranh con vật lên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and number của Unit 16 “My pets”, GV chiếu tranh con vật lên màn hình và mở bản nghe
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Find and circle the words, GV chiếu bảng chữ cái lên màn hình, HS lên khoanh các từ chỉ con vật nuôi
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -25714,7 +26035,9 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Look, listen and repeat của Unit 17 “Our toys”, GV chiếu tranh các đồ chơi lên màn hình và mở bản nghe mẫu tên đồ chơi
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi ghép tranh, GV chiếu các mảnh tranh đồ chơi bị xáo trộn; bốn nhóm lên ghép thành bức tranh hoàn chỉnh
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -25782,7 +26105,8 @@
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở phần Warm-up trò chơi Guessing and Choosing, GV chiếu bốn tranh đồ chơi lên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and repeat của Unit 17 “Our toys”, GV chiếu tranh đồ chơi và mở bản nghe mẫu mẫu câu Whose toy is it? – It's…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Guessing and Choosing, GV chiếu bốn tranh đồ chơi lên màn hình; HS chọn tranh rồi đặt câu hỏi để đoán
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -25851,7 +26175,9 @@
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and number của Unit 17, GV chiếu tranh đồ chơi lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS nối tranh với số thứ tự
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Find and circle the words, GV chiếu bảng chữ cái lên màn hình, HS lên khoanh các từ chỉ đồ chơi
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -25919,7 +26245,8 @@
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Look, listen and repeat của Unit 18 “Playing and doing”.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Look, listen and repeat của Unit 18 “Playing and doing”, GV chiếu tranh các bạn đang làm việc gì đó và mở bản nghe mẫu câu ở thì hiện tại tiếp…
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Warm-up, GV chiếu bài hát Head, shoulders, knees and toes có lời chạy trên màn hình để cả lớp vừa hát vừa làm động tác
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -25988,7 +26315,9 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and repeat của Unit 18, GV chiếu tranh và mở bản nghe mẫu mẫu câu What is he doing? – He's…
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Pass the ball, GV mở nhạc và chiếu mẫu câu lên màn hình; khi nhạc dừng, bạn cầm bóng nhìn mẫu câu để hỏi đáp với bạn bên cạnh
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -26056,7 +26385,8 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở phần Warm-up trò chơi Find and circle the words, GV chiếu bảng chữ cái lên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and number của Unit 18 “Playing and doing”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS nối tranh với số thứ tự
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Find and circle the words, GV chiếu bảng chữ cái lên màn hình, HS lên khoanh các từ chỉ hoạt động
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -26125,7 +26455,9 @@
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Look, listen and repeat của Unit 19 “Outdoor activities”, GV chiếu tranh các hoạt động ngoài trời và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Warm-up, GV chiếu bài hát quen thuộc có lời chạy trên màn hình để cả lớp vừa hát vừa làm động tác
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -26193,7 +26525,8 @@
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Listen and repeat của Unit 19 “Outdoor activities”, GV chiếu tranh và mở bản nghe mẫu mẫu câu Let's…, dừng sau mỗi lượt.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and repeat của Unit 19 “Outdoor activities”, GV chiếu tranh và mở bản nghe mẫu mẫu câu Let's…
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Pass the ball, GV mở nhạc và chiếu mẫu câu lên màn hình; khi nhạc dừng, bạn cầm bóng nhìn mẫu câu để rủ bạn bên cạnh cùng chơi
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -26262,7 +26595,9 @@
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and number của Unit 19, GV chiếu tranh hoạt động ngoài trời lên màn hình và mở bản nghe
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Find and circle the words, GV chiếu bảng chữ cái lên màn hình, HS lên khoanh các từ chỉ hoạt động ngoài trời
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -26330,7 +26665,8 @@
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Ở phần Warm-up, GV chiếu bài hát quen thuộc.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Look, listen and repeat của Unit 20 “At the zoo”, GV chiếu tranh vườn thú và mở bản nghe mẫu tên các con vật
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Warm-up, GV chiếu bài hát quen thuộc có lời chạy trên màn hình để cả lớp vừa hát vừa làm động tác
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -26399,7 +26735,9 @@
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and repeat của Unit 20, GV chiếu tranh con vật kèm đặc điểm và mở bản nghe mẫu câu mô tả
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Pass the ball, GV mở nhạc và chiếu mẫu câu mô tả lên màn hình; khi nhạc dừng, bạn cầm bóng nhìn mẫu câu để tả một con vật
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -26467,7 +26805,8 @@
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Listen and number của Unit 20 “At the zoo”, GV chiếu tranh con vật lên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Listen and number của Unit 20 “At the zoo”, GV chiếu tranh con vật lên màn hình và mở bản nghe
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần Warm-up trò chơi Find and circle the words, GV chiếu bảng chữ cái lên màn hình, HS lên khoanh các từ chỉ con vật
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -28620,7 +28959,8 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Mở đầu bài “Dụng cụ và vật liệu làm thủ công”, GV chiếu ảnh chụp gần kéo, bút chì.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Mở đầu bài “Dụng cụ và vật liệu làm thủ công”, GV chiếu ảnh chụp gần kéo, bút chì, thước, hồ dán, giấy màu
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác nối dụng cụ với công việc: HS kéo kéo về ô cắt, hồ về ô dán
 KNS: KN lao động tự phục vụ: làm việc cẩn thận, kiên trì hoàn thành sản phẩm.</t>
         </is>
       </c>
@@ -28681,7 +29021,8 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở hoạt động Thực hành, GV chiếu lại đúng bước mà nhiều bạn còn lúng túng, dừng hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khởi động bài “Làm đồ dùng học tập”, GV chiếu video hướng dẫn làm một đồ dùng học tập đơn giản, cho chạy chậm và dừng ở từng bước gấp, cắt
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Thực hành, GV chiếu lại đúng bước mà nhiều bạn còn lúng túng, dừng hình để cả lớp nhìn kĩ
 STEM: Sáng tạo đồ dùng học tập (Công nghệ – Mĩ thuật) — dạy thay cho tiết này.
 KNS: KN lao động tự phục vụ: làm việc cẩn thận, kiên trì hoàn thành sản phẩm.</t>
         </is>
@@ -28894,7 +29235,8 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở hoạt động Thực hành, GV chiếu lại đúng bước mà nhiều bạn còn lúng túng.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khởi động bài “Làm đồ chơi”, GV chiếu video hướng dẫn làm một món đồ chơi đơn giản, cho chạy chậm và dừng ở từng bước gấp, cắt, dán
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Thực hành, GV chiếu lại đúng bước mà nhiều bạn còn lúng túng và dừng hình; HS đối chiếu sản phẩm của mình với hình trên màn hình để tìm ra…
 KNS: KN lao động tự phục vụ: làm việc cẩn thận, kiên trì hoàn thành sản phẩm.</t>
         </is>
       </c>
@@ -29288,7 +29630,9 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>QPAN: Cho HS nghe/hát bài hát về chú bộ đội, về Đội; giáo dục tự hào về truyền thống dân tộc; rèn tính kỉ luật, tinh thần đoàn kết.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở tiết học hát Quốc ca Việt Nam, GV mở bản thu Quốc ca chính thức và video về ý nghĩa lá cờ Tổ quốc; HS nghe trọn bài một lượt
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở lại bản thu theo từng câu hát, dừng đúng chỗ HS hay hát sai nhịp hoặc sai lời để cả lớp nghe kĩ rồi hát lại theo
+QPAN: Cho HS nghe/hát bài hát về chú bộ đội, về Đội; giáo dục tự hào về truyền thống dân tộc; rèn tính kỉ luật, tinh thần đoàn kết.</t>
         </is>
       </c>
     </row>
@@ -29322,7 +29666,8 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.2 CB1a: HS chia sẻ cảm nhận của mình trong nhóm, biết nghe bạn nói hết ý rồi mới nêu ý kiến.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở tiết học hát Quốc ca Việt Nam, GV mở bản thu Quốc ca chính thức và video về ý nghĩa lá cờ Tổ quốc; HS nghe trọn bài một lượt
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở lại bản thu theo từng câu hát, dừng đúng chỗ HS hay hát sai nhịp hoặc sai lời để cả lớp nghe kĩ rồi hát lại theo
 QPAN: Cho HS nghe/hát bài hát về chú bộ đội, về Đội; giáo dục tự hào về truyền thống dân tộc; rèn tính kỉ luật, tinh thần đoàn kết.</t>
         </is>
       </c>
@@ -29357,7 +29702,9 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>QPAN: Chọn bài hát ca ngợi quê hương, đất nước, hoà bình; liên hệ truyền thống chống giặc ngoại xâm, gương dũng cảm của thiếu niên, nhi đồng và Bà mẹ Việt Nam anh hùng.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở tiết học nhạc cụ ma-ra-cát, GV mở bản thu âm sắc của ma-ra-cát cùng thanh phách, song loan, trống nhỏ cho HS nghe mà không nhìn thấy nhạc cụ
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV chiếu mẫu tiết tấu và mở nhạc nền chậm dần đều; HS gõ ma-ra-cát theo mẫu, khi lệch phách thì GV dừng nhạc đúng chỗ đó cho các em nghe lại và tự…
+QPAN: Chọn bài hát ca ngợi quê hương, đất nước, hoà bình; liên hệ truyền thống chống giặc ngoại xâm, gương dũng cảm của thiếu niên, nhi đồng và Bà mẹ Việt Nam anh hùng.</t>
         </is>
       </c>
     </row>
@@ -29424,7 +29771,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở tiết học bài hát “Vui đến trường”, GV mở bản thu bài hát và chiếu hình tiết tấu phóng to; HS nghe trọn bài một lượt
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở lại bản thu theo từng câu hát, dừng đúng chỗ HS hay hát sai lời hoặc sai nhịp để cả lớp nghe kĩ rồi hát lại theo</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -29454,7 +29806,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở tiết học bài hát “Vui đến trường”, GV mở bản thu bài hát và chiếu hình tiết tấu phóng to; HS nghe trọn bài một lượt
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở lại bản thu theo từng câu hát, dừng đúng chỗ HS hay hát sai lời hoặc sai nhịp để cả lớp nghe kĩ rồi hát lại theo</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -29553,7 +29910,12 @@
           <t>13</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở tiết học bài hát “Khúc nhạc trên nương xa”, GV mở bản thu bài hát và chiếu tranh các nhạc cụ dân tộc; HS nghe trọn bài một lượt
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở lại bản thu theo từng câu hát, dừng đúng chỗ HS hay hát sai lời hoặc sai nhịp để cả lớp nghe kĩ rồi hát lại theo</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -29585,7 +29947,8 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Mở nhạc nền rồi dừng đúng chỗ HS gõ lệch phách để cả lớp nghe lại.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở tiết học bài hát “Khúc nhạc trên nương xa”, GV mở bản thu bài hát và chiếu tranh các nhạc cụ dân tộc; HS nghe trọn bài một lượt
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở lại bản thu theo từng câu hát, dừng đúng chỗ HS hay hát sai lời hoặc sai nhịp để cả lớp nghe kĩ rồi hát lại theo</t>
         </is>
       </c>
     </row>
@@ -29750,7 +30113,12 @@
           <t>19</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động mở đầu bài hát “Đón xuân về”, GV chiếu hình ảnh về ngày Tết và mở bản hát mẫu từ học liệu số của bộ sách
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động luyện hát, GV dùng điện thoại ghi âm phần hát của từng tổ rồi mở lại cho cả lớp nghe</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -29780,7 +30148,12 @@
           <t>20</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động mở đầu bài hát “Đón xuân về”, GV chiếu hình ảnh về ngày Tết và mở bản hát mẫu từ học liệu số của bộ sách
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động luyện hát, GV dùng điện thoại ghi âm phần hát của từng tổ rồi mở lại cho cả lớp nghe</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -29880,7 +30253,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động mở đầu bài hát “Đẹp mãi tuổi thơ”, GV mở bản hát mẫu từ học liệu số của bộ sách, cho nghe trọn một lượt rồi nghe lại từng câu
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động luyện hát, GV ghi âm phần hát của từng tổ rồi mở lại cho cả lớp nghe; các em tự nhận ra chỗ hát chưa đúng cao độ hoặc vào nhịp…</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -29910,7 +30288,12 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động mở đầu bài hát “Đẹp mãi tuổi thơ”, GV mở bản hát mẫu từ học liệu số của bộ sách, cho nghe trọn một lượt rồi nghe lại từng câu
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động luyện hát, GV ghi âm phần hát của từng tổ rồi mở lại cho cả lớp nghe; các em tự nhận ra chỗ hát chưa đúng cao độ hoặc vào nhịp…</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -29940,7 +30323,12 @@
           <t>25</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động mở đầu trò chơi Ban nhạc lớp Ba, GV trình chiếu các hình tiết tấu đã học kèm hình nhạc cụ minh hoạ
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động luyện tập, GV ghi âm phần gõ đệm của từng nhóm rồi mở lại cho cả lớp nghe; các em tự nhận ra chỗ gõ chưa đều</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -30005,7 +30393,12 @@
           <t>27</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động mở đầu bài hát “Con chim non”, GV mở bản thu bài Chúc mừng kèm hình ảnh minh hoạ để HS nghe, vận động theo nhịp và cảm nhận nhịp ba
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động luyện hát, GV ghi âm phần hát của từng tổ rồi mở lại cho cả lớp nghe; các em tự nhận ra chỗ hát chưa đúng nhịp ba hoặc lấy hơi…</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -30035,7 +30428,12 @@
           <t>28</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động mở đầu bài hát “Con chim non”, GV mở bản thu bài Chúc mừng kèm hình ảnh minh hoạ để HS nghe, vận động theo nhịp và cảm nhận nhịp ba
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động luyện hát, GV ghi âm phần hát của từng tổ rồi mở lại cho cả lớp nghe; các em tự nhận ra chỗ hát chưa đúng nhịp ba hoặc lấy hơi…</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -30134,7 +30532,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động mở đầu bài hát “Hè về vui quá”, GV mở bản thu bài Mùa hoa phượng nở kèm hình ảnh mùa hè để HS nghe, vỗ tay theo nhịp
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động luyện hát, GV ghi âm phần hát của từng tổ rồi mở lại cho cả lớp nghe; các em tự nhận ra chỗ hát chưa đúng cao độ hoặc lấy hơi…</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -30166,7 +30569,8 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>NLS-ST (Cơ bản 1): Ở hoạt động nhạc cụ, GV chiếu hình tiết tấu lên màn hình.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động mở đầu bài hát “Hè về vui quá”, GV mở bản thu bài Mùa hoa phượng nở kèm hình ảnh mùa hè để HS nghe, vỗ tay theo nhịp
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động luyện hát, GV ghi âm phần hát của từng tổ rồi mở lại cho cả lớp nghe; các em tự nhận ra chỗ hát chưa đúng cao độ hoặc lấy hơi…</t>
         </is>
       </c>
     </row>

--- a/assets/docs/lop3/KHDH ca khoi - Lop 3.xlsx
+++ b/assets/docs/lop3/KHDH ca khoi - Lop 3.xlsx
@@ -1377,7 +1377,8 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Trước khi đọc bài “Đi học vui sao / Nói và nghe: Tới lớp, tới trường”, GV chiếu 2–3 hình ảnh hoặc.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước khi đọc bài “Đi học vui sao / Nói và nghe: Tới lớp, tới trường”, GV chiếu 2–3 hình ảnh hoặc một đoạn video ngắn về sự vật
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV mở bản đọc mẫu do phát thanh viên thể hiện cho HS nghe một lần, dừng lại để HS nhận ra chỗ người đọc ngắt hơi, nhấn giọng
 QTE: QTE: liên hệ quyền được học tập, vui chơi và được yêu thương của trẻ em qua nhân vật, chi tiết trong bài đọc.</t>
         </is>
       </c>
@@ -1460,7 +1461,9 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>QTE: QTE: liên hệ quyền được học tập, vui chơi và được yêu thương của trẻ em qua nhân vật, chi tiết trong bài đọc.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước khi đọc bài “Con đường đến trường / Viết: Ôn chữ viết hoa D, Đ”, GV chiếu 2–3 hình ảnh hoặc một đoạn video ngắn về sự vật
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV mở bản đọc mẫu do phát thanh viên thể hiện cho HS nghe một lần, dừng lại để HS nhận ra chỗ người đọc ngắt hơi, nhấn giọng
+QTE: QTE: liên hệ quyền được học tập, vui chơi và được yêu thương của trẻ em qua nhân vật, chi tiết trong bài đọc.</t>
         </is>
       </c>
     </row>

--- a/assets/docs/lop3/KHDH ca khoi - Lop 3.xlsx
+++ b/assets/docs/lop3/KHDH ca khoi - Lop 3.xlsx
@@ -7057,7 +7057,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS chỉ được trên sơ đồ đường di chuyển của tổ mình trong “Biến đổi đội hình từ một hàng ngang thành hai, ba hàng ngang và ngược lại”.
+          <t>Năng lực số 1.1 CB1b: HS chỉ được trên sơ đồ đường di chuyển của tổ mình trong “Biến đổi đội hình từ một hàng dọc thành hai, ba hàng dọc và ngược lại”.
 KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
@@ -7331,8 +7331,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS chỉ được trên sơ đồ đường di chuyển của tổ mình trong “Biến đổi đội hình từ một hàng ngang thành hai, ba hàng ngang và ngược lại”.
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7399,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.4 CB1a: HS đọc được bảng theo dõi phần đội hình đội ngũ đã học và nói được mình tiến bộ ở nội dung nào.
+          <t>Năng lực số 1.1 CB1b: HS xem clip mẫu động tác đi đều, đứng lại trên màn hình rồi chỉ ra nhịp đánh tay và nhịp bước chân.
 KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
@@ -7572,11 +7571,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu clip mẫu “Động tác vươn thở và động tác tay” đã chọn sẵn, cho chạy chậm.</t>
-        </is>
-      </c>
+      <c r="H19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -7640,11 +7635,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu clip mẫu “Động tác chân, động tác lườn, động tác bụng” đã chọn sẵn, cho chạy chậm.</t>
-        </is>
-      </c>
+      <c r="H21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -7738,11 +7729,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát clip chạy chậm và nói được một chi tiết trong “Động tác phối hợp, động tác nhảy, động tác điều hoà” mà mình hay làm sai.</t>
-        </is>
-      </c>
+      <c r="H24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -7772,11 +7759,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.4 CB1a: HS đọc được bảng theo dõi phần đội hình đội ngũ và bài thể dục phát triển chung và nói được mình tiến bộ ở nội dung nào.</t>
-        </is>
-      </c>
+      <c r="H25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -7877,7 +7860,7 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát clip chạy chậm và nói được một chi tiết trong “Bài tập phối hợp di chuyển vượt qua chướng ngại vật trên đường thẳng” mà mình hay làm sai.
+          <t>Năng lực số 3.1 CB1a: HS xem lại clip mình thực hiện “Bài tập phối hợp di chuyển vượt qua chướng ngại vật trên đường thẳng” cho chạy chậm và chỉ ra được chỗ mình làm chưa đúng.
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -8015,7 +7998,7 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát clip chạy chậm và nói được một chi tiết trong “Bài tập phối hợp di chuyển vượt qua chướng ngại vật trên đường gấp khúc” mà mình hay làm sai.
+          <t>Năng lực số 3.1 CB1a: HS xem lại clip mình thực hiện “Bài tập phối hợp di chuyển vượt qua chướng ngại vật trên đường gấp khúc” cho chạy chậm và chỉ ra được chỗ mình làm chưa đúng.
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -8084,7 +8067,7 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB1a: HS xem lại clip mình thực hiện “Bài tập phối hợp di chuyển vượt qua chướng ngại vật trên đường gấp khúc” cho chạy chậm và chỉ ra được chỗ mình làm chưa đúng.
+          <t>Năng lực số 1.1 CB1b: HS xem sơ đồ đường gấp khúc trên màn hình, chỉ ra chỗ phải giảm tốc độ để đổi hướng an toàn.
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -8119,7 +8102,8 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>Năng lực số 1.1 CB1b: HS xem sơ đồ đường gấp khúc trên màn hình, chỉ ra chỗ phải giảm tốc độ để đổi hướng an toàn.
+KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -8250,11 +8234,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.4 CB1a: HS đọc được bảng theo dõi phần đội hình đội ngũ và bài thể dục phát triển chung và nói được mình tiến bộ ở nội dung nào.</t>
-        </is>
-      </c>
+      <c r="H39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -8287,7 +8267,7 @@
       <c r="H40" s="4" t="inlineStr">
         <is>
           <t>Điều chỉnh: chuyển ôn tập, đánh giá cuối HKI về tuần 18; các bài của chủ đề lùi tương ứng sang đầu HKII.
-Năng lực số 1.1 CB1b: HS quan sát clip chạy chậm và nói được một chi tiết trong “Bài tập phối hợp di chuyển vượt qua chướng ngại vật trên địa hình tự nhiên” mà mình hay làm sai.
+Năng lực số 3.1 CB1a: HS xem lại clip mình thực hiện “Bài tập phối hợp di chuyển vượt qua chướng ngại vật trên địa hình tự nhiên” cho chạy chậm và chỉ ra được chỗ mình làm chưa đúng.
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -8356,7 +8336,7 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB1a: HS xem lại clip mình thực hiện “Bài tập phối hợp di chuyển vượt qua chướng ngại vật trên địa hình tự nhiên” cho chạy chậm và chỉ ra được chỗ mình làm chưa đúng.
+          <t>Năng lực số 1.1 CB1b: HS xem ảnh chụp khu vực sân tập trên màn hình, chỉ ra chỗ gồ ghề cần chú ý.
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -8391,7 +8371,8 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>Năng lực số 1.1 CB1b: HS xem ảnh chụp khu vực sân tập trên màn hình, chỉ ra chỗ gồ ghề cần chú ý.
+KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -8494,8 +8475,7 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát clip chạy chậm và nói được một chi tiết trong “Bài tập tại chỗ tung - bắt bóng bằng hai tay” mà mình hay làm sai.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -8632,8 +8612,7 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát clip chạy chậm và nói được một chi tiết trong “Bài tập di chuyển tung - bắt bóng bằng hai tay” mà mình hay làm sai.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8744,7 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát clip chạy chậm và nói được một chi tiết trong “Bài tập bổ trợ với bóng” mà mình hay làm sai.</t>
+          <t>Năng lực số 3.1 CB1a: HS xem lại clip mình thực hiện “Bài tập bổ trợ với bóng” cho chạy chậm và chỉ ra được chỗ mình làm chưa đúng.</t>
         </is>
       </c>
     </row>
@@ -8797,11 +8776,7 @@
           <t>52</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu clip mẫu “Bài tập bổ trợ với bóng” đã chọn sẵn, cho chạy chậm.</t>
-        </is>
-      </c>
+      <c r="H55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -8895,11 +8870,7 @@
           <t>55</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát clip chạy chậm và nói được một chi tiết trong “Động tác dẫn bóng theo hướng thẳng, dẫn bóng đổi hướng” mà mình hay làm sai.</t>
-        </is>
-      </c>
+      <c r="H58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -8929,11 +8900,7 @@
           <t>56</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu clip mẫu “Động tác dẫn bóng theo hướng thẳng, dẫn bóng đổi hướng” đã chọn sẵn, cho chạy chậm.</t>
-        </is>
-      </c>
+      <c r="H59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -8963,11 +8930,7 @@
           <t>57</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.4 CB1a: HS đọc được bảng theo dõi phần đội hình đội ngũ và bài thể dục phát triển chung và nói được mình tiến bộ ở nội dung nào.</t>
-        </is>
-      </c>
+      <c r="H60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -9031,11 +8994,7 @@
           <t>59</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát clip chạy chậm và nói được một chi tiết trong “Động tác chuyền bóng bằng hai tay trước ngực” mà mình hay làm sai.</t>
-        </is>
-      </c>
+      <c r="H62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -9067,7 +9026,7 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu clip mẫu “Động tác chuyền bóng bằng hai tay trước ngực” đã chọn sẵn, cho chạy chậm.</t>
+          <t>Năng lực số 1.1 CB1b: HS xem clip chậm động tác chuyền bóng, chỉ ra vị trí tay và hướng đẩy bóng.</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9058,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr"/>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 1.1 CB1b: HS xem clip chậm động tác chuyền bóng, chỉ ra vị trí tay và hướng đẩy bóng.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -9129,11 +9092,7 @@
           <t>62</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1b: HS xem clip chậm động tác chuyền bóng, chỉ ra vị trí tay và hướng đẩy bóng.</t>
-        </is>
-      </c>
+      <c r="H65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -9233,7 +9192,7 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS nêu được 2-3 điều luật của trò chơi gắn với “Bài tập phối hợp dẫn bóng - ném bóng rổ hai tay trước ngực” sau khi xem hình sân và bảng luật.</t>
+          <t>Năng lực số 1.1 CB1b: HS xem clip chậm pha dẫn bóng – dừng – ném, chỉ ra chỗ phải hạ thấp trọng tâm.</t>
         </is>
       </c>
     </row>
@@ -9393,11 +9352,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.4 CB1a: HS đọc bảng theo dõi số lần ném trúng rổ của tổ mình qua các tiết và nói được mình tiến bộ ở đâu.</t>
-        </is>
-      </c>
+      <c r="H73" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/assets/docs/lop3/KHDH ca khoi - Lop 3.xlsx
+++ b/assets/docs/lop3/KHDH ca khoi - Lop 3.xlsx
@@ -9446,7 +9446,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ GIỚI THIỆU VỀ MÌNH</t>
+          <t>Chủ đề: Tự giới thiệu về mình</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ GIỚI THIỆU VỀ MÌNH</t>
+          <t>Chủ đề: Tự giới thiệu về mình</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ GIỚI THIỆU VỀ MÌNH</t>
+          <t>Chủ đề: Tự giới thiệu về mình</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ GIỚI THIỆU VỀ MÌNH</t>
+          <t>Chủ đề: Tự giới thiệu về mình</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ GIỚI THIỆU VỀ MÌNH</t>
+          <t>Chủ đề: Tự giới thiệu về mình</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ GIỚI THIỆU VỀ MÌNH</t>
+          <t>Chủ đề: Tự giới thiệu về mình</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ GIỚI THIỆU VỀ MÌNH</t>
+          <t>Chủ đề: Tự giới thiệu về mình</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ GIỚI THIỆU VỀ MÌNH</t>
+          <t>Chủ đề: Tự giới thiệu về mình</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ GIỚI THIỆU VỀ MÌNH</t>
+          <t>Chủ đề: Tự giới thiệu về mình</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ GIỚI THIỆU VỀ MÌNH</t>
+          <t>Chủ đề: Tự giới thiệu về mình</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ GIỚI THIỆU VỀ MÌNH</t>
+          <t>Chủ đề: Tự giới thiệu về mình</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ GIỚI THIỆU VỀ MÌNH</t>
+          <t>Chủ đề: Tự giới thiệu về mình</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG ĐẸP</t>
+          <t>Chủ đề: Nếp sống đẹp</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG ĐẸP</t>
+          <t>Chủ đề: Nếp sống đẹp</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG ĐẸP</t>
+          <t>Chủ đề: Nếp sống đẹp</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG ĐẸP</t>
+          <t>Chủ đề: Nếp sống đẹp</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -9996,7 +9996,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG ĐẸP</t>
+          <t>Chủ đề: Nếp sống đẹp</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG ĐẸP</t>
+          <t>Chủ đề: Nếp sống đẹp</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG ĐẸP</t>
+          <t>Chủ đề: Nếp sống đẹp</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG ĐẸP</t>
+          <t>Chủ đề: Nếp sống đẹp</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG ĐẸP</t>
+          <t>Chủ đề: Nếp sống đẹp</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG ĐẸP</t>
+          <t>Chủ đề: Nếp sống đẹp</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG ĐẸP</t>
+          <t>Chủ đề: Nếp sống đẹp</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG ĐẸP</t>
+          <t>Chủ đề: Nếp sống đẹp</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI TRƯỜNG EM YÊU</t>
+          <t>Chủ đề: Mái trường em yêu</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI TRƯỜNG EM YÊU</t>
+          <t>Chủ đề: Mái trường em yêu</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -10339,7 +10339,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI TRƯỜNG EM YÊU</t>
+          <t>Chủ đề: Mái trường em yêu</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -10374,7 +10374,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI TRƯỜNG EM YÊU</t>
+          <t>Chủ đề: Mái trường em yêu</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -10408,7 +10408,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI TRƯỜNG EM YÊU</t>
+          <t>Chủ đề: Mái trường em yêu</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI TRƯỜNG EM YÊU</t>
+          <t>Chủ đề: Mái trường em yêu</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI TRƯỜNG EM YÊU</t>
+          <t>Chủ đề: Mái trường em yêu</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI TRƯỜNG EM YÊU</t>
+          <t>Chủ đề: Mái trường em yêu</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI TRƯỜNG EM YÊU</t>
+          <t>Chủ đề: Mái trường em yêu</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI TRƯỜNG EM YÊU</t>
+          <t>Chủ đề: Mái trường em yêu</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI TRƯỜNG EM YÊU</t>
+          <t>Chủ đề: Mái trường em yêu</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI TRƯỜNG EM YÊU</t>
+          <t>Chủ đề: Mái trường em yêu</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN NHÀ CỬA NGĂN NẮP, SẠCH ĐẸP</t>
+          <t>Chủ đề: Giữ gìn nhà cửa ngăn nắp, sạch đẹp</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -10713,7 +10713,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN NHÀ CỬA NGĂN NẮP, SẠCH ĐẸP</t>
+          <t>Chủ đề: Giữ gìn nhà cửa ngăn nắp, sạch đẹp</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
@@ -10748,7 +10748,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN NHÀ CỬA NGĂN NẮP, SẠCH ĐẸP</t>
+          <t>Chủ đề: Giữ gìn nhà cửa ngăn nắp, sạch đẹp</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
@@ -10782,7 +10782,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN NHÀ CỬA NGĂN NẮP, SẠCH ĐẸP</t>
+          <t>Chủ đề: Giữ gìn nhà cửa ngăn nắp, sạch đẹp</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr"/>
@@ -10816,7 +10816,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN NHÀ CỬA NGĂN NẮP, SẠCH ĐẸP</t>
+          <t>Chủ đề: Giữ gìn nhà cửa ngăn nắp, sạch đẹp</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN NHÀ CỬA NGĂN NẮP, SẠCH ĐẸP</t>
+          <t>Chủ đề: Giữ gìn nhà cửa ngăn nắp, sạch đẹp</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
@@ -10885,7 +10885,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN NHÀ CỬA NGĂN NẮP, SẠCH ĐẸP</t>
+          <t>Chủ đề: Giữ gìn nhà cửa ngăn nắp, sạch đẹp</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN NHÀ CỬA NGĂN NẮP, SẠCH ĐẸP</t>
+          <t>Chủ đề: Giữ gìn nhà cửa ngăn nắp, sạch đẹp</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN NHÀ CỬA NGĂN NẮP, SẠCH ĐẸP</t>
+          <t>Chủ đề: Giữ gìn nhà cửa ngăn nắp, sạch đẹp</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN NHÀ CỬA NGĂN NẮP, SẠCH ĐẸP</t>
+          <t>Chủ đề: Giữ gìn nhà cửa ngăn nắp, sạch đẹp</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
@@ -11023,7 +11023,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN NHÀ CỬA NGĂN NẮP, SẠCH ĐẸP</t>
+          <t>Chủ đề: Giữ gìn nhà cửa ngăn nắp, sạch đẹp</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN NHÀ CỬA NGĂN NẮP, SẠCH ĐẸP</t>
+          <t>Chủ đề: Giữ gìn nhà cửa ngăn nắp, sạch đẹp</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIA ĐÌNH YÊU THƯƠNG</t>
+          <t>Chủ đề: Gia đình yêu thương</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIA ĐÌNH YÊU THƯƠNG</t>
+          <t>Chủ đề: Gia đình yêu thương</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIA ĐÌNH YÊU THƯƠNG</t>
+          <t>Chủ đề: Gia đình yêu thương</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -11195,7 +11195,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIA ĐÌNH YÊU THƯƠNG</t>
+          <t>Chủ đề: Gia đình yêu thương</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
@@ -11230,7 +11230,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIA ĐÌNH YÊU THƯƠNG</t>
+          <t>Chủ đề: Gia đình yêu thương</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
@@ -11265,7 +11265,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIA ĐÌNH YÊU THƯƠNG</t>
+          <t>Chủ đề: Gia đình yêu thương</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
@@ -11607,7 +11607,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr"/>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -11707,7 +11707,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr"/>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr"/>
@@ -11947,7 +11947,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr"/>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr"/>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr"/>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr"/>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr"/>
@@ -12153,7 +12153,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr"/>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: ĂN UỐNG AN TOÀN, HỢP VỆ SINH</t>
+          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr"/>
@@ -12219,7 +12219,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: LÀM BẠN VỚI THIÊN NHIÊN</t>
+          <t>Chủ đề: Làm bạn với thiên nhiên</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr"/>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: LÀM BẠN VỚI THIÊN NHIÊN</t>
+          <t>Chủ đề: Làm bạn với thiên nhiên</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr"/>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: LÀM BẠN VỚI THIÊN NHIÊN</t>
+          <t>Chủ đề: Làm bạn với thiên nhiên</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: LÀM BẠN VỚI THIÊN NHIÊN</t>
+          <t>Chủ đề: Làm bạn với thiên nhiên</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: LÀM BẠN VỚI THIÊN NHIÊN</t>
+          <t>Chủ đề: Làm bạn với thiên nhiên</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr"/>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: LÀM BẠN VỚI THIÊN NHIÊN</t>
+          <t>Chủ đề: Làm bạn với thiên nhiên</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr"/>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: LÀM BẠN VỚI THIÊN NHIÊN</t>
+          <t>Chủ đề: Làm bạn với thiên nhiên</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr"/>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: LÀM BẠN VỚI THIÊN NHIÊN</t>
+          <t>Chủ đề: Làm bạn với thiên nhiên</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: LÀM BẠN VỚI THIÊN NHIÊN</t>
+          <t>Chủ đề: Làm bạn với thiên nhiên</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr"/>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: LÀM BẠN VỚI THIÊN NHIÊN</t>
+          <t>Chủ đề: Làm bạn với thiên nhiên</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr"/>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: LÀM BẠN VỚI THIÊN NHIÊN</t>
+          <t>Chủ đề: Làm bạn với thiên nhiên</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr"/>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: LÀM BẠN VỚI THIÊN NHIÊN</t>
+          <t>Chủ đề: Làm bạn với thiên nhiên</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÌM HIỂU THẾ GIỚI NGHỀ NGHIỆP</t>
+          <t>Chủ đề: Tìm hiểu thế giới nghề nghiệp</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr"/>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÌM HIỂU THẾ GIỚI NGHỀ NGHIỆP</t>
+          <t>Chủ đề: Tìm hiểu thế giới nghề nghiệp</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr"/>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÌM HIỂU THẾ GIỚI NGHỀ NGHIỆP</t>
+          <t>Chủ đề: Tìm hiểu thế giới nghề nghiệp</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr"/>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÌM HIỂU THẾ GIỚI NGHỀ NGHIỆP</t>
+          <t>Chủ đề: Tìm hiểu thế giới nghề nghiệp</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr"/>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÌM HIỂU THẾ GIỚI NGHỀ NGHIỆP</t>
+          <t>Chủ đề: Tìm hiểu thế giới nghề nghiệp</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr"/>
@@ -12816,7 +12816,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÌM HIỂU THẾ GIỚI NGHỀ NGHIỆP</t>
+          <t>Chủ đề: Tìm hiểu thế giới nghề nghiệp</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr"/>
@@ -12851,7 +12851,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÌM HIỂU THẾ GIỚI NGHỀ NGHIỆP</t>
+          <t>Chủ đề: Tìm hiểu thế giới nghề nghiệp</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr"/>
@@ -12886,7 +12886,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÌM HIỂU THẾ GIỚI NGHỀ NGHIỆP</t>
+          <t>Chủ đề: Tìm hiểu thế giới nghề nghiệp</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr"/>
@@ -12922,7 +12922,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÌM HIỂU THẾ GIỚI NGHỀ NGHIỆP</t>
+          <t>Chủ đề: Tìm hiểu thế giới nghề nghiệp</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr"/>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÌM HIỂU THẾ GIỚI NGHỀ NGHIỆP</t>
+          <t>Chủ đề: Tìm hiểu thế giới nghề nghiệp</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr"/>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÌM HIỂU THẾ GIỚI NGHỀ NGHIỆP</t>
+          <t>Chủ đề: Tìm hiểu thế giới nghề nghiệp</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr"/>
@@ -13020,7 +13020,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÌM HIỂU THẾ GIỚI NGHỀ NGHIỆP</t>
+          <t>Chủ đề: Tìm hiểu thế giới nghề nghiệp</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr"/>
@@ -29429,7 +29429,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: LỄ HỘI ÂM THANH</t>
+          <t>Chủ đề 1: Lễ hội âm thanh</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -29463,7 +29463,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: LỄ HỘI ÂM THANH</t>
+          <t>Chủ đề 1: Lễ hội âm thanh</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -29497,7 +29497,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: LỄ HỘI ÂM THANH</t>
+          <t>Chủ đề 1: Lễ hội âm thanh</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -29531,7 +29531,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: LỄ HỘI ÂM THANH</t>
+          <t>Chủ đề 1: Lễ hội âm thanh</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -29566,7 +29566,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: EM YÊU TỔ QUỐC VIỆT NAM</t>
+          <t>Chủ đề 2: Em yêu Tổ quốc Việt Nam</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -29602,7 +29602,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: EM YÊU TỔ QUỐC VIỆT NAM</t>
+          <t>Chủ đề 2: Em yêu Tổ quốc Việt Nam</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -29638,7 +29638,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: EM YÊU TỔ QUỐC VIỆT NAM</t>
+          <t>Chủ đề 2: Em yêu Tổ quốc Việt Nam</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -29674,7 +29674,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: EM YÊU TỔ QUỐC VIỆT NAM</t>
+          <t>Chủ đề 2: Em yêu Tổ quốc Việt Nam</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -29709,7 +29709,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: VUI ĐẾN TRƯỜNG</t>
+          <t>Chủ đề 3: Vui đến trường</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -29744,7 +29744,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: VUI ĐẾN TRƯỜNG</t>
+          <t>Chủ đề 3: Vui đến trường</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: VUI ĐẾN TRƯỜNG</t>
+          <t>Chủ đề 3: Vui đến trường</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -29813,7 +29813,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: VUI ĐẾN TRƯỜNG</t>
+          <t>Chủ đề 3: Vui đến trường</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -29848,7 +29848,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: EM YÊU LÀN ĐIỆU DÂN CA</t>
+          <t>Chủ đề 4: Em yêu làn điệu dân ca</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -29883,7 +29883,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: EM YÊU LÀN ĐIỆU DÂN CA</t>
+          <t>Chủ đề 4: Em yêu làn điệu dân ca</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -29918,7 +29918,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: EM YÊU LÀN ĐIỆU DÂN CA</t>
+          <t>Chủ đề 4: Em yêu làn điệu dân ca</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -29952,7 +29952,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: EM YÊU LÀN ĐIỆU DÂN CA</t>
+          <t>Chủ đề 4: Em yêu làn điệu dân ca</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -30051,7 +30051,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: ĐÓN XUÂN VỀ</t>
+          <t>Chủ đề 5: Đón xuân về</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: ĐÓN XUÂN VỀ</t>
+          <t>Chủ đề 5: Đón xuân về</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -30121,7 +30121,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: ĐÓN XUÂN VỀ</t>
+          <t>Chủ đề 5: Đón xuân về</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -30156,7 +30156,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: ĐÓN XUÂN VỀ</t>
+          <t>Chủ đề 5: Đón xuân về</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -30191,7 +30191,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: ĐẸP MÃI TUỔI THƠ</t>
+          <t>Chủ đề 6: Đẹp mãi tuổi thơ</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: ĐẸP MÃI TUỔI THƠ</t>
+          <t>Chủ đề 6: Đẹp mãi tuổi thơ</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -30261,7 +30261,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: ĐẸP MÃI TUỔI THƠ</t>
+          <t>Chủ đề 6: Đẹp mãi tuổi thơ</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -30296,7 +30296,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: ĐẸP MÃI TUỔI THƠ</t>
+          <t>Chủ đề 6: Đẹp mãi tuổi thơ</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -30331,7 +30331,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 7: ÂM NHẠC NƯỚC NGOÀI</t>
+          <t>Chủ đề 7: Âm nhạc nước ngoài</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -30366,7 +30366,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 7: ÂM NHẠC NƯỚC NGOÀI</t>
+          <t>Chủ đề 7: Âm nhạc nước ngoài</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -30401,7 +30401,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 7: ÂM NHẠC NƯỚC NGOÀI</t>
+          <t>Chủ đề 7: Âm nhạc nước ngoài</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -30435,7 +30435,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 7: ÂM NHẠC NƯỚC NGOÀI</t>
+          <t>Chủ đề 7: Âm nhạc nước ngoài</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 8: VUI ĐÓN HÈ</t>
+          <t>Chủ đề 8: Vui đón hè</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -30505,7 +30505,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 8: VUI ĐÓN HÈ</t>
+          <t>Chủ đề 8: Vui đón hè</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -30540,7 +30540,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 8: VUI ĐÓN HÈ</t>
+          <t>Chủ đề 8: Vui đón hè</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
